--- a/academias/Química - Estadisticos 20212.xlsx
+++ b/academias/Química - Estadisticos 20212.xlsx
@@ -688,22 +688,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -720,22 +723,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -752,22 +758,25 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -784,22 +793,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -816,22 +828,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -848,22 +863,25 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>
@@ -1511,22 +1529,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1543,22 +1564,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1575,22 +1599,25 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1607,22 +1634,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1639,22 +1669,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1671,22 +1704,25 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Química - Estadisticos 20212.xlsx
+++ b/academias/Química - Estadisticos 20212.xlsx
@@ -1014,22 +1014,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>32.14</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.1</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1078,22 +1081,25 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1436,7 +1442,7 @@
         <v>3.57</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1494,19 +1500,19 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Química - Estadisticos 20212.xlsx
+++ b/academias/Química - Estadisticos 20212.xlsx
@@ -700,13 +700,13 @@
         <v>9.380000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -735,13 +735,13 @@
         <v>4.55</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -805,13 +805,13 @@
         <v>10.81</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -840,13 +840,13 @@
         <v>6.25</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -875,13 +875,13 @@
         <v>9.09</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -950,22 +950,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>51.43</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>48.57</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.9</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -982,22 +985,25 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>48.65</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>51.35</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1026,13 +1032,13 @@
         <v>32.14</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1">
-        <v>32.14</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1049,22 +1055,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>53.66</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>46.34</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1116,22 +1125,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1148,22 +1160,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1180,22 +1195,25 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1212,22 +1230,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>13.51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1244,22 +1265,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1276,22 +1300,25 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F12">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>11.36</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1372,7 +1399,7 @@
         <v>17.14</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1407,7 +1434,7 @@
         <v>5.41</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1477,7 +1504,7 @@
         <v>12.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1535,25 +1562,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>9.380000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1570,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>95.45</v>
+        <v>90.91</v>
       </c>
       <c r="H8" s="1">
-        <v>4.55</v>
+        <v>9.09</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1605,19 +1632,19 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1640,25 +1667,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>89.19</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>10.81</v>
+        <v>13.51</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1675,25 +1702,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>93.75</v>
+        <v>90.63</v>
       </c>
       <c r="H11" s="1">
-        <v>6.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1710,25 +1737,25 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>90.91</v>
+        <v>88.64</v>
       </c>
       <c r="H12" s="1">
-        <v>9.09</v>
+        <v>11.36</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Química - Estadisticos 20212.xlsx
+++ b/academias/Química - Estadisticos 20212.xlsx
@@ -950,25 +950,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>51.43</v>
+        <v>82.86</v>
       </c>
       <c r="H2" s="1">
-        <v>48.57</v>
+        <v>17.14</v>
       </c>
       <c r="I2" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>48.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,25 +985,25 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>48.65</v>
+        <v>91.89</v>
       </c>
       <c r="H3" s="1">
-        <v>51.35</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>45.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1020,25 +1020,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>67.86</v>
+        <v>92.86</v>
       </c>
       <c r="H4" s="1">
-        <v>32.14</v>
+        <v>7.14</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1055,25 +1055,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>53.66</v>
+        <v>87.8</v>
       </c>
       <c r="H5" s="1">
-        <v>46.34</v>
+        <v>12.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>46.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1090,25 +1090,25 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H6" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1387,19 +1387,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>82.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>17.14</v>
+        <v>14.29</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1422,19 +1422,19 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>3.57</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1492,19 +1492,19 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>12.2</v>
+        <v>7.32</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1527,19 +1527,19 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1562,19 +1562,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1597,19 +1597,19 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>90.91</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>9.09</v>
+        <v>6.82</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>3.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1667,19 +1667,19 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H10" s="1">
-        <v>13.51</v>
+        <v>10.81</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1702,19 +1702,19 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H11" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1737,19 +1737,19 @@
         <v>44</v>
       </c>
       <c r="E12">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>88.64</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>11.36</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
         <v>0</v>
